--- a/data/蝦皮.xlsx
+++ b/data/蝦皮.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE1"/>
+  <dimension ref="A1:BE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,6 +716,621 @@
           <t>備註</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>260201GQBYRHUM</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>min.ru.huang</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-02-01 00:07</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>270</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>45</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>270</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>5534878671</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>【黑色】吊帶款▶短版,L</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>18324832208</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>5534878671_18324832208</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>135</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>HFC01001</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>HFC01001-TS-SH-BK-L</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>臺南市</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>新營區</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>蝦皮店到店</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>寄件</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>信用卡</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>2026-02-02 23:59</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>TW267073050545R</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>2026-02-01 00:07</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>2026-02-01 19:22</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>2026-02-05 00:59</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>260201GQBYRHUM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>min.ru.huang</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-02-01 00:07</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>270</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>45</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>270</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>16</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>5534878671</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>〖黑色〗背心款▶短版,L</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>175839177445</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>5534878671_175839177445</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>135</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>HFC01001</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>HFC01001-WS-SH-BK-L</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>臺南市</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>新營區</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>蝦皮店到店</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>寄件</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>信用卡</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>2026-02-02 23:59</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>TW267073050545R</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>2026-02-01 00:07</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>2026-02-01 19:22</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>2026-02-05 00:59</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>260201GRHS02SN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>jamlalabob</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-02-01 00:28</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>300</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>45</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>300</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>18</v>
+      </c>
+      <c r="U4" t="n">
+        <v>18</v>
+      </c>
+      <c r="V4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>13960892663</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>煙粉色,M</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>200864883928</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>13960892663_200864883928</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>HFE03002-PK-M</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>新北市</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>三重區</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>蝦皮店到店</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>寄件</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>貨到付款</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>2026-02-02 23:59</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>TW266452265661V</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>2026-02-01 00:28</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>2026-02-01 19:22</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>2026-02-08 21:38</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/蝦皮.xlsx
+++ b/data/蝦皮.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE4"/>
+  <dimension ref="A1:BE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,621 +716,6 @@
           <t>備註</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>260201GQBYRHUM</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>min.ru.huang</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-02-01 00:07</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>270</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>45</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>270</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>16</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2.50%</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心</t>
-        </is>
-      </c>
-      <c r="AA2" t="n">
-        <v>5534878671</v>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>【黑色】吊帶款▶短版,L</t>
-        </is>
-      </c>
-      <c r="AC2" t="n">
-        <v>18324832208</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>5534878671_18324832208</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>135</v>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>HFC01001</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>HFC01001-TS-SH-BK-L</t>
-        </is>
-      </c>
-      <c r="AI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>臺南市</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>新營區</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>蝦皮店到店</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>寄件</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>信用卡</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>2026-02-02 23:59</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>TW267073050545R</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>2026-02-01 00:07</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>2026-02-01 19:22</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>2026-02-05 00:59</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>260201GQBYRHUM</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>min.ru.huang</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-02-01 00:07</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>270</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>45</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>270</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>16</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2.50%</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心</t>
-        </is>
-      </c>
-      <c r="AA3" t="n">
-        <v>5534878671</v>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>〖黑色〗背心款▶短版,L</t>
-        </is>
-      </c>
-      <c r="AC3" t="n">
-        <v>175839177445</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>5534878671_175839177445</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>135</v>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>HFC01001</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>HFC01001-WS-SH-BK-L</t>
-        </is>
-      </c>
-      <c r="AI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>臺南市</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>新營區</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>蝦皮店到店</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>寄件</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>信用卡</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>2026-02-02 23:59</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>TW267073050545R</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>2026-02-01 00:07</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>2026-02-01 19:22</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>2026-02-05 00:59</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>260201GRHS02SN</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>jamlalabob</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-02-01 00:28</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>300</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>45</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>300</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>18</v>
-      </c>
-      <c r="U4" t="n">
-        <v>18</v>
-      </c>
-      <c r="V4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2.50%</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女</t>
-        </is>
-      </c>
-      <c r="AA4" t="n">
-        <v>13960892663</v>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>煙粉色,M</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>200864883928</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>13960892663_200864883928</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>HFE03002</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>HFE03002-PK-M</t>
-        </is>
-      </c>
-      <c r="AI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>新北市</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>三重區</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>蝦皮店到店</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>寄件</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>貨到付款</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>2026-02-02 23:59</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>TW266452265661V</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>2026-02-01 00:28</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>2026-02-01 19:22</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>2026-02-08 21:38</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/蝦皮.xlsx
+++ b/data/蝦皮.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE1"/>
+  <dimension ref="A1:BE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,6 +716,621 @@
           <t>備註</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>260201GQBYRHUM</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>min.ru.huang</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-02-01 00:07</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>270</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>45</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>270</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>16</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>5534878671</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>【黑色】吊帶款▶短版,L</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>18324832208</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>5534878671_18324832208</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>135</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>HFC01001</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>HFC01001-TS-SH-BK-L</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>臺南市</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>新營區</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>蝦皮店到店</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>寄件</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>信用卡</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>2026-02-02 23:59</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>TW267073050545R</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>2026-02-01 00:07</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>2026-02-01 19:22</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>2026-02-05 00:59</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>260201GQBYRHUM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>min.ru.huang</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-02-01 00:07</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>270</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>45</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>270</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>16</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>5534878671</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>〖黑色〗背心款▶短版,L</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>175839177445</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>5534878671_175839177445</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>135</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>HFC01001</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>HFC01001-WS-SH-BK-L</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>臺南市</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>新營區</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>蝦皮店到店</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>寄件</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>信用卡</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>2026-02-02 23:59</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>TW267073050545R</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>2026-02-01 00:07</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>2026-02-01 19:22</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>2026-02-05 00:59</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>260201GRHS02SN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>jamlalabob</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-02-01 00:28</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>300</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>45</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>300</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>18</v>
+      </c>
+      <c r="U4" t="n">
+        <v>18</v>
+      </c>
+      <c r="V4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>[高回購口碑款🍑超好穿不夾臀] 高腰內褲 女生內褲 莫代爾 女內著 內褲女</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>13960892663</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>煙粉色,M</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>200864883928</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>13960892663_200864883928</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>HFE03002</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>HFE03002-PK-M</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>新北市</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>三重區</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>蝦皮店到店</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>寄件</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>貨到付款</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>2026-02-02 23:59</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>TW266452265661V</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>2026-02-01 00:28</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>2026-02-01 19:22</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>2026-02-08 21:38</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/蝦皮.xlsx
+++ b/data/蝦皮.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE1"/>
+  <dimension ref="A1:BE17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,6 +716,2498 @@
           <t>備註</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>260101T9JAVCHM</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>不成立</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>系統自動判定訂單不成立，原因 : 無法順利配送</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>tracy700302</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-01-01 02:07</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>768</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>CHIE599;2RJMUYS3VA</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>53000881766</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>【男款】黑色｜上衣+長褲套裝,XL</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>297128417355</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>53000881766_297128417355</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>499</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>399</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>HMH02001-BK-XL</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>屏東縣</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>萬丹鄉</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>蝦皮店到店</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>寄件</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>貨到付款</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>2026-01-02 23:59</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>TW267941820032W</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>2026-01-01 02:07</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>2026-01-02 19:21</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>260101T9JAVCHM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>不成立</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>系統自動判定訂單不成立，原因 : 無法順利配送</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>tracy700302</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-01-01 02:07</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>768</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CHIE599;2RJMUYS3VA</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>[雙面磨毛🔥一穿即暖]發熱衣男 發熱衣女 發熱衣 保暖衣 發熱褲 保暖套裝</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>53000881766</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>【女款】灰色｜上衣+長褲套裝,M</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>390079183183</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>53000881766_390079183183</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>499</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>399</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>HFH02001-GY-M</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>屏東縣</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>萬丹鄉</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>蝦皮店到店</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>寄件</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>貨到付款</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>2026-01-02 23:59</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>TW267941820032W</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>2026-01-01 02:07</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>2026-01-02 19:21</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>260101U289VMH1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>不成立</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>被買家取消，原因 : 改變心意(例如:不想買了,發現更便宜的價格....)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>t9725164</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-01-01 09:29</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>358</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>29565881384</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>黑色｜立領,XL</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>89676798786</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>29565881384_89676798786</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>199</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>179</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>HFA02001-MN-BK-XL</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>高雄市</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>三民區</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>蝦皮店到店</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>貨到付款</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>2026-01-02 23:59</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>2026-01-01 09:29</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>260101UQC2FXC5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>已同意申請</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>sarli13</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-01-01 15:46</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>270</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>45</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>5534878671</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>【黑色】吊帶款▶短版,M</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>18324832207</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>5534878671_18324832207</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>135</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>HFC01001</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>HFC01001-TS-SH-BK-M</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>高雄市</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>鼓山區</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>蝦皮店到店</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>寄件</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>貨到付款</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>2026-01-02 23:59</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>TW262060233155Q</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>2026-01-01 15:46</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>2026-01-02 19:20</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>2026-01-12 18:19</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>退貨運費45</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>260101UQC2FXC5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>已同意申請</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>sarli13</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-01-01 15:46</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>270</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>45</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>[夏天必備☀️打底神器]內搭襯裙 背帶裙 細肩帶睡衣 長版背心</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>5534878671</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>【白色】吊帶款▶短版 ❗️微透❗️,M</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>18324832225</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>5534878671_18324832225</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>135</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>HFC01001</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>HFC01001-TS-SH-WH-M</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>高雄市</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>鼓山區</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>蝦皮店到店</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>寄件</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>貨到付款</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>2026-01-02 23:59</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>TW262060233155Q</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>2026-01-01 15:46</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>2026-01-02 19:20</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>2026-01-12 18:19</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>退貨運費45</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>260101VGTQ5TTD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>已同意申請</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>yicheng__chen</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-01-01 23:22</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>523</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>60</v>
+      </c>
+      <c r="K7" t="n">
+        <v>45</v>
+      </c>
+      <c r="L7" t="n">
+        <v>73</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CHIE399</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>3970007224</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>【素色】黑灰色,XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>241366564465</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>3970007224_241366564465</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>79</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>HME03002-SO-BK-XL</t>
+        </is>
+      </c>
+      <c r="AI7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>5 件 9.5折</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>臺北市</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>中山區</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>蝦皮店到店 - 隔日到貨</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>寄件</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>信用卡</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>2026-01-02 20:00</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>TW264487853921T</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>2026-01-01 23:22</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>2026-01-02 19:23</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>2026-01-04 21:48</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>260101VGTQ5TTD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>已同意申請</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>yicheng__chen</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-01-01 23:22</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>523</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>60</v>
+      </c>
+      <c r="K8" t="n">
+        <v>45</v>
+      </c>
+      <c r="L8" t="n">
+        <v>73</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CHIE399</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲</t>
+        </is>
+      </c>
+      <c r="AA8" t="n">
+        <v>3970007224</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>〖條紋〗深藍色,XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>241366564469</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>3970007224_241366564469</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>79</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>HME03002-ST-DN-XL</t>
+        </is>
+      </c>
+      <c r="AI8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>5 件 9.5折</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>臺北市</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>中山區</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>蝦皮店到店 - 隔日到貨</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>寄件</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>信用卡</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>2026-01-02 20:00</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>TW264487853921T</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>2026-01-01 23:22</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>2026-01-02 19:23</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>2026-01-04 21:48</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>260101VGTQ5TTD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>已同意申請</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>yicheng__chen</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-01-01 23:22</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>523</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>60</v>
+      </c>
+      <c r="K9" t="n">
+        <v>45</v>
+      </c>
+      <c r="L9" t="n">
+        <v>73</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CHIE399</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>[會呼吸的內褲🌬柔順舒適彩紗棉] 莫代爾內褲 男內褲 平口內褲男 男生內褲</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>3970007224</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>【素色】深藍色,XL ➜建議80-85KG</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>241366564453</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>3970007224_241366564453</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>79</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>79</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>HME03002</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>HME03002-SO-DN-XL</t>
+        </is>
+      </c>
+      <c r="AI9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>臺北市</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>中山區</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>蝦皮店到店 - 隔日到貨</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>寄件</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>信用卡</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>2026-01-02 20:00</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>TW264487853921T</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>2026-01-01 23:22</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>2026-01-02 19:23</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>2026-01-04 21:48</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>260111RDUTKB7X</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>fanghsinkuo</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-01-11 22:06</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>229</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>45</v>
+      </c>
+      <c r="K10" t="n">
+        <v>45</v>
+      </c>
+      <c r="L10" t="n">
+        <v>89</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>LHERS46S37</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>[粉底級遮瑕💎寒流級超厚絨]保暖褲襪 光腿神器 刷毛褲襪 褲襪 光腿 厚褲襪</t>
+        </is>
+      </c>
+      <c r="AA10" t="n">
+        <v>3260877596</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>140克微中絨｜參考穿著溫度15-20℃,膚色</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>252224043997</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>3260877596_252224043997</t>
+        </is>
+      </c>
+      <c r="AE10" t="n">
+        <v>99</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>99</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>HFF02001</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>HFF02001-SK-140G</t>
+        </is>
+      </c>
+      <c r="AI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>高雄市</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>鳳山區</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>蝦皮店到店</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>寄件</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>貨到付款</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>2026-01-12 23:59</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>TW266154678098Z</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>2026-01-11 22:06</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>2026-01-12 14:42</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>2026-01-24 00:36</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>退貨運費45</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>260111RDUTKB7X</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>已同意申請</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>fanghsinkuo</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-01-11 22:06</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>229</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>45</v>
+      </c>
+      <c r="K11" t="n">
+        <v>45</v>
+      </c>
+      <c r="L11" t="n">
+        <v>89</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>LHERS46S37</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>[秋冬打底必備🍁萬用三種領型]內搭長袖 打底衣 高領打底衣 內搭上衣 立領上衣 高領上衣</t>
+        </is>
+      </c>
+      <c r="AA11" t="n">
+        <v>29565881384</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>黑色｜高領,M</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>89676798808</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>29565881384_89676798808</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
+        <v>199</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>159</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>HFA02001-TN-BK-M</t>
+        </is>
+      </c>
+      <c r="AI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>高雄市</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>鳳山區</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>****</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>蝦皮店到店</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>寄件</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>貨到付款</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>2026-01-12 23:59</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>TW266154678098Z</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>2026-01-11 22:06</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>2026-01-12 14:42</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>2026-01-24 00:36</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>退貨運費45</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1.260101T9JAVCHM：未取貨</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>日報表可直接刪除不列出；不扣庫存，不計入出庫</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2.260101U289VMH1：出貨前取消訂單</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>日報表可直接刪除不列出；不扣庫存，不計入出庫</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3.260101UQC2FXC5：整單退貨</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>日報表需列出，需列出K欄_退貨運費，若退貨運費顯示0也需要列出；不扣庫存，不計入出庫</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4.260101VGTQ5TTD：部份退貨</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>日報表需列出，要看AI欄_數量＆AJ欄_退貨數量差額，AI與AJ無差額代表該項全退貨，有差額為實際退貨數量；需列出K欄_退貨運費，若退貨運費顯示0也需要列出；退貨部份不扣庫存，不計入出庫。此範例 HME03002-ST-DN-XL 購買3，退貨2，等於此訂單實際成交為 HME03002-ST-DN-XL *1，庫存及出庫需計入 HME03002-ST-DN-XL *1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>5.260111RDUTKB7X：部份退貨</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>日報表需列出，購買不同品項，僅退貨一個品項，另一個未退貨品項的E欄_退貨 / 退款狀態則為空白，不會顯示「已同意申請」文字；需列出K欄_退貨運費，若退貨運費顯示0也需要列出；退貨部份不扣庫存，不計入出庫。此範例 HFA02001-TN-BK-M 全退貨，HFF02001-SK-140G 保留，等於此訂單實際成交為 HFF02001-SK-140G *1，庫存及出庫需計入 HFF02001-SK-140G *1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/蝦皮.xlsx
+++ b/data/蝦皮.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,299 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>訂單編號</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>訂單狀態</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>熱門商品</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>不成立原因</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>退貨 / 退款狀態</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>買家帳號</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>訂單成立日期</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>商品總價</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>買家支付運費</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>蝦皮補助運費</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>退貨運費</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>買家總支付金額</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>蝦皮補貼金額</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>蝦幣折抵</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>銀行信用卡活動折抵</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>優惠代碼</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>賣家負擔優惠券</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>賣家負擔蝦幣回饋券</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>蝦皮負擔優惠券</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>成交手續費</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>其他服務費</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>金流與系統處理費</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>分期付款期數</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>金流與系統處理費率</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>成交手續費規則名稱</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>商品名稱</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>商品ID</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>商品選項名稱</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>規格ID</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>蝦皮商品編碼 (商品ID_規格ID)</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>商品原價</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>商品活動價格</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>主商品貨號</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>商品選項貨號</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>數量</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>退貨數量</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>促銷組合指標</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>蝦皮促銷組合折扣:促銷組合標籤</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>收件地址</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>收件者電話
-(若您是自行配送請使用後方蝦皮專線和包裹查詢碼聯繫買家)</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>蝦皮專線和包裹查詢碼 
-(請複製下方完整編號提供給您配合的物流商當做聯絡電話)</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>取件門市店號</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>城市</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>行政區</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>郵遞區號</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>收件者姓名</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>寄送方式</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>出貨方式</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>備貨時間</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>付款方式</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>最晚出貨日期</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>包裹查詢號碼</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>買家付款時間</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>實際出貨時間</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>訂單完成時間</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>買家備註</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>備註</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>